--- a/単価変更管理システム.xlsx
+++ b/単価変更管理システム.xlsx
@@ -886,7 +886,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3. 「新仕入値」「仕入適用日」「新売価」「売価適用日」「備考」「担当者」を入力します。</t>
+          <t>3. 「新仕入値」「仕入適用日」「新売価」「売価適用日」「備考」を入力します。「担当者」は藤田・中岡・白石からプルダウンで選択します。</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       <formula>AND($N2="済",$O2&lt;&gt;"完了")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="C2:C301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=商品リスト</formula1>
     </dataValidation>
@@ -12147,6 +12147,9 @@
     </dataValidation>
     <dataValidation sqref="O2:O301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未,完了"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"藤田,中岡,白石"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/単価変更管理システム.xlsx
+++ b/単価変更管理システム.xlsx
@@ -12673,7 +12673,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>サンダイヤ㈱1</t>
+          <t>サンダイヤ㈱</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr"/>

--- a/単価変更管理システム.xlsx
+++ b/単価変更管理システム.xlsx
@@ -19513,16 +19513,16 @@
       <formula1>"単価変更,新規登録"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=商品リスト</formula1>
+      <formula1>商品リスト</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=荷姿リスト</formula1>
+      <formula1>荷姿リスト</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=仕入先リスト</formula1>
+      <formula1>仕入先リスト</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=得意先リスト</formula1>
+      <formula1>得意先リスト</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未,済"</formula1>
@@ -26646,13 +26646,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C2:C201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=仕入先リスト</formula1>
+      <formula1>仕入先リスト</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=得意先リスト</formula1>
+      <formula1>得意先リスト</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=荷姿リスト</formula1>
+      <formula1>荷姿リスト</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28090,7 +28090,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=管理番号リスト</formula1>
+      <formula1>管理番号リスト</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -28457,7 +28457,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=管理番号リスト</formula1>
+      <formula1>管理番号リスト</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
